--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38657-2026 artfynd.xlsx
+++ b/artfynd/A 38657-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759873</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136759808</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
